--- a/Config/Datas/talent.xlsx
+++ b/Config/Datas/talent.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="talent" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="talent_level" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,25 +435,10 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>prereq_node_ids</t>
+          <t>max_level</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
-        <is>
-          <t>unlock_conds</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>unlock_costs</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>stat_bonuses</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
         <is>
           <t>passive_skill_id</t>
         </is>
@@ -476,25 +462,10 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>(list#sep=;),int</t>
+          <t>int</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
-        <is>
-          <t>(list#sep=;),CommonCheckCond</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>(list#sep=|),TalentUnlockCost</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>(list#sep=|),TalentStatBonus</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -521,26 +492,6 @@
           <t>c</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -560,25 +511,10 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>prereq_node_ids</t>
+          <t>max_level</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
-        <is>
-          <t>unlock_conds</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>unlock_costs</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>stat_bonuses</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
         <is>
           <t>passive_skill_id</t>
         </is>
@@ -593,19 +529,10 @@
           <t>天分-魅力根基</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0,0,0,0,0,"",""</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>2,1200</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="B6" t="n">
@@ -616,27 +543,10 @@
           <t>天分-护甲理解</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0,0,0,0,0,"",""</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>wood,2</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>4,800</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="B7" t="n">
@@ -647,27 +557,10 @@
           <t>天分-意志魅力</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0,0,0,0,0,"",""</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>stick,1</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>3,600</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="B8" t="n">
@@ -678,27 +571,10 @@
           <t>天分-双防雏形</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0,0,0,0,0,"",""</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>wood,1|stick,1</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>5,700|4,400</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="B9" t="n">
@@ -709,6 +585,284 @@
           <t>天分-统合</t>
         </is>
       </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>node_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>prereq_node_ids</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>unlock_conds</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>unlock_costs</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>stat_bonuses</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>(list#sep=;),int</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>(list#sep=;),CommonCheckCond</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>(list#sep=|),TalentUnlockCost</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>(list#sep=|),TalentStatBonus</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>##group</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>node_id</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>prereq_node_ids</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>unlock_conds</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>unlock_costs</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>stat_bonuses</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0,0,0,0,0,"",""</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2,1200</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0,0,0,0,0,"",""</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>wood,2</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0,0,0,0,0,"",""</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>stick,1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0,0,0,0,0,"",""</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>wood,1|stick,1</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>5,700|4,400</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>2;3</t>
@@ -729,7 +883,6 @@
           <t>2,500|5,300</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Config/Datas/talent.xlsx
+++ b/Config/Datas/talent.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowHeight="17655" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="talent" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="49">
   <si>
     <t>##var</t>
   </si>
@@ -187,14 +187,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -650,148 +643,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1341,7 +1334,7 @@
     <col min="4" max="4" width="9.75" customWidth="1"/>
     <col min="5" max="5" width="11.375" customWidth="1"/>
     <col min="6" max="6" width="11.25" customWidth="1"/>
-    <col min="7" max="7" width="15.375" customWidth="1"/>
+    <col min="7" max="8" width="15.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1415,9 +1408,7 @@
       <c r="G3" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>10</v>
-      </c>
+      <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
@@ -1552,7 +1543,6 @@
       <c r="C11">
         <v>1</v>
       </c>
-      <c r="D11"/>
       <c r="H11" t="s">
         <v>46</v>
       </c>
@@ -1564,7 +1554,6 @@
       <c r="C12">
         <v>1</v>
       </c>
-      <c r="D12"/>
       <c r="H12" t="s">
         <v>47</v>
       </c>
@@ -1576,7 +1565,6 @@
       <c r="C13">
         <v>1</v>
       </c>
-      <c r="D13"/>
       <c r="H13" t="s">
         <v>48</v>
       </c>

--- a/Config/Datas/talent.xlsx
+++ b/Config/Datas/talent.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="62">
   <si>
     <t>##var</t>
   </si>
@@ -69,7 +69,7 @@
     <t>路径</t>
   </si>
   <si>
-    <t>天分-魅力根基</t>
+    <t>魅力四射</t>
   </si>
   <si>
     <t>default</t>
@@ -99,6 +99,9 @@
     <t>level</t>
   </si>
   <si>
+    <t>#comment</t>
+  </si>
+  <si>
     <t>prereq_node_ids</t>
   </si>
   <si>
@@ -132,7 +135,46 @@
     <t>0,0,0,0,0,"",""</t>
   </si>
   <si>
-    <t>2,1200</t>
+    <t>desire_shard,100</t>
+  </si>
+  <si>
+    <t>3,5000</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>desire_shard,1000</t>
+  </si>
+  <si>
+    <t>3,10000</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>desire_shard,5000</t>
+  </si>
+  <si>
+    <t>3,15000</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>desire_shard,10000</t>
+  </si>
+  <si>
+    <t>3,20000</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>desire_shard,50000</t>
+  </si>
+  <si>
+    <t>3,25000</t>
   </si>
   <si>
     <t>1</t>
@@ -148,9 +190,6 @@
   </si>
   <si>
     <t>3,600</t>
-  </si>
-  <si>
-    <t>2</t>
   </si>
   <si>
     <t>wood,1|stick,1</t>
@@ -788,8 +827,10 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1216,7 +1257,7 @@
       <c r="D5">
         <v>1</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="3" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1230,7 +1271,7 @@
       <c r="D6">
         <v>1</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="3" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1244,7 +1285,7 @@
       <c r="D7">
         <v>1</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="3" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1258,7 +1299,7 @@
       <c r="D8">
         <v>1</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="3" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1272,7 +1313,7 @@
       <c r="D9">
         <v>1</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" s="3" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1286,7 +1327,7 @@
       <c r="D11">
         <v>1</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" s="3" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1300,7 +1341,7 @@
       <c r="D12">
         <v>1</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E12" s="3" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1314,7 +1355,7 @@
       <c r="D13">
         <v>1</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="E13" s="3" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1327,246 +1368,405 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <dimension ref="A1:I18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="3" max="3" width="9.625" customWidth="1"/>
-    <col min="4" max="4" width="9.75" customWidth="1"/>
-    <col min="5" max="5" width="11.375" customWidth="1"/>
-    <col min="6" max="6" width="11.25" customWidth="1"/>
-    <col min="7" max="8" width="15.375" customWidth="1"/>
+    <col min="4" max="4" width="14.875" customWidth="1"/>
+    <col min="5" max="5" width="14.25" customWidth="1"/>
+    <col min="6" max="6" width="18.75" customWidth="1"/>
+    <col min="7" max="7" width="30" customWidth="1"/>
+    <col min="8" max="9" width="15.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" t="s">
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" t="s">
+      <c r="I1" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="D2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="1" t="s">
         <v>31</v>
       </c>
       <c r="H2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
-      <c r="A3" t="s">
+    <row r="3" spans="1:9">
+      <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C3" t="s">
+      <c r="B3" s="1"/>
+      <c r="C3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="1"/>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" t="s">
+      <c r="I3" s="2"/>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="D4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="1" t="s">
         <v>26</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="I4" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1">
+        <v>1</v>
+      </c>
+      <c r="C5" s="1">
+        <v>1</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F5" t="s">
-        <v>32</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="F5" s="1" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="B6">
+      <c r="G5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1">
         <v>2</v>
       </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="C6" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F6" t="s">
-        <v>36</v>
-      </c>
-      <c r="G6" t="s">
+      <c r="F6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I6" s="1"/>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1">
+        <v>3</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I7" s="1"/>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1">
+        <v>4</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="I8" s="1"/>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1">
+        <v>5</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I9" s="1"/>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1">
+        <v>2</v>
+      </c>
+      <c r="C11" s="1">
+        <v>1</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I11" s="1"/>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1">
+        <v>3</v>
+      </c>
+      <c r="C12" s="1">
+        <v>1</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I12" s="1"/>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1">
+        <v>4</v>
+      </c>
+      <c r="C13" s="1">
+        <v>1</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="B7">
-        <v>3</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7" t="s">
-        <v>35</v>
-      </c>
-      <c r="E7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F7" t="s">
-        <v>38</v>
-      </c>
-      <c r="G7" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="B8">
-        <v>4</v>
-      </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E8" t="s">
-        <v>33</v>
-      </c>
-      <c r="F8" t="s">
-        <v>41</v>
-      </c>
-      <c r="G8" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="B9">
+      <c r="F13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I13" s="1"/>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1">
         <v>5</v>
       </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9" t="s">
-        <v>43</v>
-      </c>
-      <c r="E9" t="s">
-        <v>33</v>
-      </c>
-      <c r="F9" t="s">
-        <v>44</v>
-      </c>
-      <c r="G9" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="B11">
+      <c r="C14" s="1">
+        <v>1</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="I14" s="1"/>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="B16">
         <v>11</v>
       </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="H11" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="B12">
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16" t="s">
+        <v>19</v>
+      </c>
+      <c r="I16" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9">
+      <c r="B17">
         <v>12</v>
       </c>
-      <c r="C12">
-        <v>1</v>
-      </c>
-      <c r="H12" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="B13">
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17" t="s">
+        <v>20</v>
+      </c>
+      <c r="I17" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9">
+      <c r="B18">
         <v>13</v>
       </c>
-      <c r="C13">
-        <v>1</v>
-      </c>
-      <c r="H13" t="s">
-        <v>48</v>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18" t="s">
+        <v>21</v>
+      </c>
+      <c r="I18" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Datas/talent.xlsx
+++ b/Config/Datas/talent.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="63">
   <si>
     <t>##var</t>
   </si>
@@ -139,6 +139,9 @@
   </si>
   <si>
     <t>3,5000</t>
+  </si>
+  <si>
+    <t>talent_expose_charm</t>
   </si>
   <si>
     <t>2</t>
@@ -1514,7 +1517,9 @@
       <c r="H5" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="I5" s="1"/>
+      <c r="I5" s="1" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1"/>
@@ -1522,7 +1527,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>13</v>
@@ -1534,12 +1539,14 @@
         <v>34</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="I6" s="1"/>
+        <v>40</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1"/>
@@ -1547,7 +1554,7 @@
         <v>3</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>13</v>
@@ -1559,12 +1566,14 @@
         <v>34</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="I7" s="1"/>
+        <v>43</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1"/>
@@ -1572,7 +1581,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>13</v>
@@ -1584,12 +1593,14 @@
         <v>34</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="I8" s="1"/>
+        <v>46</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1"/>
@@ -1597,7 +1608,7 @@
         <v>5</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>13</v>
@@ -1609,12 +1620,14 @@
         <v>34</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I9" s="1"/>
+        <v>49</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1"/>
@@ -1639,16 +1652,16 @@
         <v>15</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>34</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I11" s="1"/>
     </row>
@@ -1664,16 +1677,16 @@
         <v>16</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>34</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I12" s="1"/>
     </row>
@@ -1689,16 +1702,16 @@
         <v>17</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>34</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I13" s="1"/>
     </row>
@@ -1714,16 +1727,16 @@
         <v>18</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>34</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I14" s="1"/>
     </row>
@@ -1738,7 +1751,7 @@
         <v>19</v>
       </c>
       <c r="I16" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="2:9">
@@ -1752,7 +1765,7 @@
         <v>20</v>
       </c>
       <c r="I17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18" spans="2:9">
@@ -1766,7 +1779,7 @@
         <v>21</v>
       </c>
       <c r="I18" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Datas/talent.xlsx
+++ b/Config/Datas/talent.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17655" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="talent_tree" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="talent" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="talent_level" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="talent_tree" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="talent" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="talent_level" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1036,7 +1036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1173,6 +1173,50 @@
       <c r="E6" t="inlineStr">
         <is>
           <t>carlisle</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>fei_tree</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>菲的估值与撬锁心得</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>UI/Prefabs/TalentTreeLayouts/FeiTalentTreeLayout</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>fei_thief</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>mei_merchant_tree</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>商人梅的商贸心得</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>UI/Prefabs/TalentTreeLayouts/MeiMerchantTalentTreeLayout</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>merchant_mei</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1231,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="14.875" customWidth="1" style="3" min="3" max="3"/>
@@ -1667,6 +1711,90 @@
       <c r="G19" t="inlineStr">
         <is>
           <t>没有训练场的流浪者，就拿路边和废墟当老师。用铁锭与亚麻布做成简陋负具，反复锤炼肉体。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>fei_tree</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>201</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>模糊估值</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>菲能看出护具大致的价值区间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>fei_tree</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>202</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>精细估值</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>菲会进一步缩小护具的价值区间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>mei_merchant_tree</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>301</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>商会议价</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>所有商铺的售价提高了5%。</t>
         </is>
       </c>
     </row>
@@ -1681,7 +1809,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="9.625" customWidth="1" style="3" min="3" max="3"/>
@@ -1898,7 +2026,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,5000</t>
+          <t>3,0,5000</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1935,7 +2063,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,10000</t>
+          <t>3,0,10000</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1972,7 +2100,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,15000</t>
+          <t>3,0,15000</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -2009,7 +2137,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,20000</t>
+          <t>3,0,20000</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2046,7 +2174,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,25000</t>
+          <t>3,0,25000</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -2096,7 +2224,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,800</t>
+          <t>4,0,800</t>
         </is>
       </c>
       <c r="I11" s="2" t="n"/>
@@ -2131,7 +2259,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,600</t>
+          <t>3,0,600</t>
         </is>
       </c>
       <c r="I12" s="2" t="n"/>
@@ -2166,7 +2294,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,700|4,400</t>
+          <t>5,0,700|4,0,400</t>
         </is>
       </c>
       <c r="I13" s="2" t="n"/>
@@ -2201,7 +2329,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,500|5,300</t>
+          <t>2,0,500|5,0,300</t>
         </is>
       </c>
       <c r="I14" s="2" t="n"/>
@@ -2283,7 +2411,7 @@
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,100</t>
+          <t>12,0,100</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
@@ -2314,7 +2442,7 @@
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,100</t>
+          <t>11,0,100</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
@@ -2345,7 +2473,7 @@
       <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,2</t>
+          <t>13,0,2</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
@@ -2372,7 +2500,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,1</t>
+          <t>13,0,1</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
@@ -2399,7 +2527,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>21,500</t>
+          <t>21,0,500</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
@@ -2426,10 +2554,84 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20,500</t>
+          <t>20,0,500</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>201</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>????</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>desire_shard,300</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>31,0,1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="n">
+        <v>202</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>????</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>desire_shard,800</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>32,0,1</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="n">
+        <v>301</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>商人梅的商贸心得</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>desire_shard,500</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>0,11,5</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Config/Datas/talent.xlsx
+++ b/Config/Datas/talent.xlsx
@@ -1387,15 +1387,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>魅力四射</t>
+          <t>基础攻击</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>default</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>将欲望转化为直接的攻击力。</t>
         </is>
       </c>
     </row>
@@ -1410,15 +1415,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>天分-护甲理解</t>
+          <t>持续强化</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>default</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>在基础攻击训练上继续投入，提升稳定输出。</t>
         </is>
       </c>
     </row>
@@ -1433,15 +1443,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>天分-意志魅力</t>
+          <t>预留节点</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>default</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>该节点尚未开放。</t>
         </is>
       </c>
     </row>
@@ -1456,15 +1471,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>天分-双防雏形</t>
+          <t>重击训练</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>default</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>强化身体与装备的配合，提升攻击上限。</t>
         </is>
       </c>
     </row>
@@ -1479,19 +1499,23 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>天分-统合</t>
+          <t>预留节点</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>default</t>
         </is>
       </c>
-    </row>
-    <row r="10"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>该节点尚未开放。</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
@@ -1503,15 +1527,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>榨汁扩展1</t>
+          <t>预留节点</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>default</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>该节点尚未开放。</t>
         </is>
       </c>
     </row>
@@ -1526,15 +1555,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>榨汁扩展2</t>
+          <t>预留节点</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>default</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>该节点尚未开放。</t>
         </is>
       </c>
     </row>
@@ -1549,15 +1583,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>榨汁扩展3</t>
+          <t>预留节点</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>default</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>该节点尚未开放。</t>
         </is>
       </c>
     </row>
@@ -2010,15 +2049,11 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>魅力四射</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0,0,0,0,0,"",""</t>
-        </is>
-      </c>
+          <t>1级攻击训练</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>desire_shard,100</t>
@@ -2026,205 +2061,185 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,0,5000</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>talent_expose_charm</t>
-        </is>
-      </c>
+          <t>20,0,600</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n"/>
       <c r="B6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>魅力四射</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,0,0,0,0,"",""</t>
-        </is>
-      </c>
+          <t>1级攻击训练</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>desire_shard,1000</t>
+          <t>desire_shard,400</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,0,10000</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>talent_expose_charm</t>
-        </is>
-      </c>
+          <t>20,0,700</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n"/>
       <c r="B7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>魅力四射</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0,0,0,0,0,"",""</t>
-        </is>
-      </c>
+          <t>1级攻击训练</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>desire_shard,5000</t>
+          <t>desire_shard,1000</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,0,15000</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>talent_expose_charm</t>
-        </is>
-      </c>
+          <t>20,0,800</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n"/>
       <c r="B8" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>魅力四射</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,0,0,0,0,"",""</t>
-        </is>
-      </c>
+          <t>2级攻击训练</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="n"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>desire_shard,10000</t>
+          <t>desire_shard,500</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,0,20000</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>talent_expose_charm</t>
-        </is>
-      </c>
+          <t>20,0,800</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n"/>
       <c r="B9" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>魅力四射</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr"/>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0,0,0,0,0,"",""</t>
-        </is>
-      </c>
+          <t>2级攻击训练</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="n"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>desire_shard,50000</t>
+          <t>desire_shard,1200</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,0,25000</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>talent_expose_charm</t>
-        </is>
-      </c>
+          <t>20,0,900</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n"/>
-      <c r="B10" s="2" t="n"/>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="n"/>
-      <c r="E10" s="2" t="n"/>
+      <c r="B10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2级攻击训练</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="F10" s="2" t="n"/>
-      <c r="G10" s="2" t="n"/>
-      <c r="H10" s="2" t="n"/>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>desire_shard,2500</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>20,0,1000</t>
+        </is>
+      </c>
       <c r="I10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n"/>
       <c r="B11" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>1</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>天分-护甲理解</t>
+          <t>4级攻击训练</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0,0,0,0,0,"",""</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="n"/>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>wood,2</t>
+          <t>desire_shard,1000</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,0,800</t>
+          <t>20,0,1000</t>
         </is>
       </c>
       <c r="I11" s="2" t="n"/>
@@ -2232,34 +2247,30 @@
     <row r="12">
       <c r="A12" s="2" t="n"/>
       <c r="B12" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>天分-意志魅力</t>
+          <t>4级攻击训练</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,0,0,0,0,"",""</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="n"/>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>stick,1</t>
+          <t>desire_shard,2500</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,0,600</t>
+          <t>20,0,1100</t>
         </is>
       </c>
       <c r="I12" s="2" t="n"/>
@@ -2270,11 +2281,11 @@
         <v>4</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>天分-双防雏形</t>
+          <t>4级攻击训练</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -2282,113 +2293,34 @@
           <t>2</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>0,0,0,0,0,"",""</t>
-        </is>
-      </c>
+      <c r="F13" s="2" t="n"/>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>wood,1|stick,1</t>
+          <t>desire_shard,5000</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,0,700|4,0,400</t>
+          <t>20,0,1200</t>
         </is>
       </c>
       <c r="I13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n"/>
-      <c r="B14" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>天分-统合</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>2;3</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0,0,0,0,0,"",""</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>gold,5</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2,0,500|5,0,300</t>
-        </is>
-      </c>
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n"/>
+      <c r="E14" s="2" t="n"/>
+      <c r="F14" s="2" t="n"/>
+      <c r="G14" s="2" t="n"/>
+      <c r="H14" s="2" t="n"/>
       <c r="I14" s="2" t="n"/>
     </row>
     <row r="15"/>
-    <row r="16">
-      <c r="B16" t="n">
-        <v>11</v>
-      </c>
-      <c r="C16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>榨汁扩展1</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>ex_zhazhi_01</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" t="n">
-        <v>12</v>
-      </c>
-      <c r="C17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>榨汁扩展2</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>ex_zhazhi_02</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" t="n">
-        <v>13</v>
-      </c>
-      <c r="C18" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>榨汁扩展3</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>ex_zhazhi_03</t>
-        </is>
-      </c>
-    </row>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="2" t="n"/>
       <c r="B19" s="2" t="n">
@@ -2411,7 +2343,7 @@
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,0,100</t>
+          <t>40,0,100</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
